--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="499">
   <si>
     <t>#</t>
   </si>
@@ -169,34 +169,28 @@
     <t>之后的及时删除</t>
   </si>
   <si>
-    <t>gx456</t>
+    <t>gx458</t>
   </si>
   <si>
     <t>4000,400,400</t>
   </si>
   <si>
-    <t>anyu456</t>
+    <t>anyu458</t>
   </si>
   <si>
     <t>20000,2000,1600</t>
   </si>
   <si>
-    <t>gx457</t>
-  </si>
-  <si>
-    <t>bc456</t>
-  </si>
-  <si>
-    <t>tt455</t>
+    <t>tt458</t>
   </si>
   <si>
     <t>9,5,9,4</t>
   </si>
   <si>
-    <t>4003,4004,4013,49</t>
-  </si>
-  <si>
-    <t>20000,2000,2000,8</t>
+    <t>4003,4004,4013,89</t>
+  </si>
+  <si>
+    <t>40000,4000,4000,12</t>
   </si>
   <si>
     <t>anyult23adu</t>
@@ -1790,12 +1784,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2911,44 +2905,10 @@
       </c>
     </row>
     <row r="17" ht="17" customHeight="1" spans="1:9">
-      <c r="C17" s="6">
-        <v>43</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>32</v>
-      </c>
+      <c r="H17" s="9"/>
     </row>
     <row r="18" ht="17" customHeight="1" spans="1:9">
-      <c r="C18" s="6">
-        <v>44</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>32</v>
-      </c>
+      <c r="H18" s="9"/>
     </row>
     <row r="19" ht="17" customHeight="1" spans="1:9">
       <c r="H19" s="9"/>
@@ -2979,16 +2939,16 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="H24" s="15" t="s">
         <v>38</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:9">
@@ -3010,19 +2970,19 @@
         <v>1</v>
       </c>
       <c r="E27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="H27" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="I27" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="H27" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:9">
@@ -3039,19 +2999,19 @@
         <v>1</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="H28" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="I28" s="11" t="s">
         <v>48</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:9">
@@ -3297,19 +3257,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="H6" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="I6" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3320,19 +3280,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="I7" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3343,19 +3303,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="I8" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3366,19 +3326,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3389,19 +3349,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="I10" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3412,19 +3372,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="I11" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3439,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F13" s="1">
         <v>5</v>
@@ -3451,7 +3411,7 @@
         <v>600</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:19">
@@ -3462,7 +3422,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F14" s="1">
         <v>5</v>
@@ -3474,7 +3434,7 @@
         <v>1200</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:19">
@@ -3485,7 +3445,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F15" s="1">
         <v>5</v>
@@ -3497,7 +3457,7 @@
         <v>1800</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:19">
@@ -3508,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F16" s="1">
         <v>5</v>
@@ -3520,7 +3480,7 @@
         <v>2400</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:9">
@@ -3531,7 +3491,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F17" s="1">
         <v>5</v>
@@ -3543,7 +3503,7 @@
         <v>3000</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:9">
@@ -3554,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F19" s="1">
         <v>3</v>
@@ -3574,7 +3534,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F20" s="1">
         <v>3</v>
@@ -3594,7 +3554,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F21" s="1">
         <v>3</v>
@@ -3614,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F22" s="1">
         <v>5</v>
@@ -3626,7 +3586,7 @@
         <v>200000</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -3637,7 +3597,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F23" s="1">
         <v>4</v>
@@ -3646,7 +3606,7 @@
         <v>9</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:9">
@@ -3657,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F25" s="1">
         <v>18</v>
@@ -3669,7 +3629,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:9">
@@ -3680,7 +3640,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F26" s="1">
         <v>18</v>
@@ -3692,7 +3652,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:9">
@@ -3703,7 +3663,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F27" s="1">
         <v>18</v>
@@ -3715,7 +3675,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:9">
@@ -3726,7 +3686,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F28" s="1">
         <v>18</v>
@@ -3738,7 +3698,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:9">
@@ -3749,7 +3709,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F29" s="1">
         <v>18</v>
@@ -3761,7 +3721,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:9">
@@ -3772,7 +3732,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F30" s="1">
         <v>18</v>
@@ -3784,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:9">
@@ -3795,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F31" s="1">
         <v>18</v>
@@ -3807,7 +3767,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:9">
@@ -3818,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F32" s="1">
         <v>18</v>
@@ -3830,7 +3790,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:9">
@@ -3844,7 +3804,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F34" s="2">
         <v>4</v>
@@ -3856,7 +3816,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -3867,7 +3827,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F35" s="2">
         <v>4</v>
@@ -3879,7 +3839,7 @@
         <v>2</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -3890,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F36" s="2">
         <v>4</v>
@@ -3902,7 +3862,7 @@
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -3913,7 +3873,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F37" s="2">
         <v>4</v>
@@ -3925,7 +3885,7 @@
         <v>4</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -3936,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F38" s="2">
         <v>4</v>
@@ -3948,7 +3908,7 @@
         <v>5</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -3959,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F39" s="2">
         <v>4</v>
@@ -3971,7 +3931,7 @@
         <v>6</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -3982,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F40" s="2">
         <v>4</v>
@@ -3994,7 +3954,7 @@
         <v>7</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:9">
@@ -4005,7 +3965,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F41" s="2">
         <v>4</v>
@@ -4017,7 +3977,7 @@
         <v>8</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:9">
@@ -4028,7 +3988,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F42" s="2">
         <v>4</v>
@@ -4040,7 +4000,7 @@
         <v>9</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:9">
@@ -4051,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F43" s="2">
         <v>4</v>
@@ -4063,7 +4023,7 @@
         <v>10</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:9">
@@ -4074,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F44" s="2">
         <v>4</v>
@@ -4086,7 +4046,7 @@
         <v>20</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:9">
@@ -4097,7 +4057,7 @@
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F45" s="2">
         <v>4</v>
@@ -4109,7 +4069,7 @@
         <v>30</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:9">
@@ -4120,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F46" s="2">
         <v>4</v>
@@ -4132,7 +4092,7 @@
         <v>40</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:9">
@@ -4152,7 +4112,7 @@
         <v>1</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F48" s="1">
         <v>18</v>
@@ -4164,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:9">
@@ -4175,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F49" s="1">
         <v>18</v>
@@ -4187,7 +4147,7 @@
         <v>2</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:9">
@@ -4198,7 +4158,7 @@
         <v>1</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F50" s="1">
         <v>18</v>
@@ -4210,7 +4170,7 @@
         <v>3</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:9">
@@ -4221,7 +4181,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F51" s="1">
         <v>18</v>
@@ -4233,7 +4193,7 @@
         <v>4</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:9">
@@ -4244,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F52" s="1">
         <v>18</v>
@@ -4256,7 +4216,7 @@
         <v>5</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:9">
@@ -4267,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F53" s="1">
         <v>18</v>
@@ -4279,7 +4239,7 @@
         <v>6</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:9">
@@ -4290,7 +4250,7 @@
         <v>1</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F54" s="1">
         <v>18</v>
@@ -4302,7 +4262,7 @@
         <v>7</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:9">
@@ -4313,7 +4273,7 @@
         <v>1</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F55" s="1">
         <v>18</v>
@@ -4325,7 +4285,7 @@
         <v>8</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" customFormat="1" customHeight="1" spans="3:9">
@@ -4336,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F56" s="1">
         <v>18</v>
@@ -4348,7 +4308,7 @@
         <v>9</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:9">
@@ -4359,7 +4319,7 @@
         <v>1</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F57" s="1">
         <v>18</v>
@@ -4371,7 +4331,7 @@
         <v>10</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:9">
@@ -4382,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F58" s="1">
         <v>18</v>
@@ -4394,7 +4354,7 @@
         <v>20</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:9">
@@ -4405,7 +4365,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F59" s="1">
         <v>18</v>
@@ -4417,7 +4377,7 @@
         <v>30</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:9">
@@ -4428,7 +4388,7 @@
         <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F60" s="1">
         <v>18</v>
@@ -4440,7 +4400,7 @@
         <v>40</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:9">
@@ -4469,7 +4429,7 @@
         <v>1</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F63" s="2">
         <v>4</v>
@@ -4481,7 +4441,7 @@
         <v>1</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:9">
@@ -4492,7 +4452,7 @@
         <v>1</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F64" s="2">
         <v>4</v>
@@ -4504,7 +4464,7 @@
         <v>1</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:9">
@@ -4515,7 +4475,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F65" s="2">
         <v>4</v>
@@ -4527,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:9">
@@ -4538,7 +4498,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F66" s="2">
         <v>4</v>
@@ -4550,7 +4510,7 @@
         <v>1</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:9">
@@ -4561,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F67" s="2">
         <v>4</v>
@@ -4573,7 +4533,7 @@
         <v>1</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:9">
@@ -4587,7 +4547,7 @@
         <v>1</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F69" s="1">
         <v>4</v>
@@ -4599,7 +4559,7 @@
         <v>1</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:9">
@@ -4610,7 +4570,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F70" s="1">
         <v>4</v>
@@ -4622,7 +4582,7 @@
         <v>2</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:9">
@@ -4633,7 +4593,7 @@
         <v>1</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F71" s="1">
         <v>4</v>
@@ -4645,7 +4605,7 @@
         <v>3</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:9">
@@ -4656,7 +4616,7 @@
         <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F72" s="1">
         <v>4</v>
@@ -4668,7 +4628,7 @@
         <v>4</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:9">
@@ -4679,7 +4639,7 @@
         <v>1</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F73" s="1">
         <v>4</v>
@@ -4691,7 +4651,7 @@
         <v>5</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:9">
@@ -4702,7 +4662,7 @@
         <v>1</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F74" s="1">
         <v>4</v>
@@ -4714,7 +4674,7 @@
         <v>6</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:9">
@@ -4725,7 +4685,7 @@
         <v>1</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F75" s="1">
         <v>4</v>
@@ -4737,7 +4697,7 @@
         <v>7</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:9">
@@ -4748,7 +4708,7 @@
         <v>1</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F76" s="1">
         <v>4</v>
@@ -4760,7 +4720,7 @@
         <v>8</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:9">
@@ -4771,7 +4731,7 @@
         <v>1</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F77" s="1">
         <v>4</v>
@@ -4783,7 +4743,7 @@
         <v>9</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:9">
@@ -4794,7 +4754,7 @@
         <v>1</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F78" s="1">
         <v>4</v>
@@ -4806,7 +4766,7 @@
         <v>10</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:9">
@@ -4817,7 +4777,7 @@
         <v>1</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F79" s="1">
         <v>4</v>
@@ -4829,7 +4789,7 @@
         <v>10</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:9">
@@ -4840,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F80" s="1">
         <v>4</v>
@@ -4852,7 +4812,7 @@
         <v>20</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:9">
@@ -4863,7 +4823,7 @@
         <v>1</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F81" s="1">
         <v>4</v>
@@ -4875,7 +4835,7 @@
         <v>30</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:9">
@@ -4886,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F82" s="1">
         <v>4</v>
@@ -4898,7 +4858,7 @@
         <v>10</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:9">
@@ -4909,7 +4869,7 @@
         <v>1</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F83" s="1">
         <v>4</v>
@@ -4921,7 +4881,7 @@
         <v>1</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:9">
@@ -4932,7 +4892,7 @@
         <v>1</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F84" s="1">
         <v>4</v>
@@ -4944,7 +4904,7 @@
         <v>1</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:9">
@@ -4955,7 +4915,7 @@
         <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F85" s="1">
         <v>4</v>
@@ -4967,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:9">
@@ -4981,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F87" s="1">
         <v>18</v>
@@ -4993,7 +4953,7 @@
         <v>1</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:9">
@@ -5004,7 +4964,7 @@
         <v>1</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F88" s="1">
         <v>18</v>
@@ -5016,7 +4976,7 @@
         <v>1</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:9">
@@ -5027,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F89" s="1">
         <v>18</v>
@@ -5039,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:9">
@@ -5050,7 +5010,7 @@
         <v>1</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F90" s="1">
         <v>18</v>
@@ -5062,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:9">
@@ -5073,7 +5033,7 @@
         <v>1</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F91" s="1">
         <v>18</v>
@@ -5085,7 +5045,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:9">
@@ -5096,7 +5056,7 @@
         <v>1</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F92" s="1">
         <v>18</v>
@@ -5108,7 +5068,7 @@
         <v>1</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:9">
@@ -5119,7 +5079,7 @@
         <v>1</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F93" s="1">
         <v>18</v>
@@ -5131,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:9">
@@ -5142,7 +5102,7 @@
         <v>1</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F94" s="1">
         <v>18</v>
@@ -5154,7 +5114,7 @@
         <v>1</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:9">
@@ -5165,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F95" s="1">
         <v>18</v>
@@ -5177,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:9">
@@ -5188,7 +5148,7 @@
         <v>1</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F96" s="1">
         <v>18</v>
@@ -5200,7 +5160,7 @@
         <v>1</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:10">
@@ -5211,7 +5171,7 @@
         <v>1</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F97" s="1">
         <v>18</v>
@@ -5223,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:10">
@@ -5234,7 +5194,7 @@
         <v>1</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F98" s="1">
         <v>18</v>
@@ -5246,7 +5206,7 @@
         <v>1</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:10">
@@ -5257,7 +5217,7 @@
         <v>1</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F99" s="1">
         <v>18</v>
@@ -5269,7 +5229,7 @@
         <v>1</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:10">
@@ -5280,7 +5240,7 @@
         <v>1</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F100" s="1">
         <v>18</v>
@@ -5292,7 +5252,7 @@
         <v>1</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:10">
@@ -5303,7 +5263,7 @@
         <v>1</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F101" s="1">
         <v>18</v>
@@ -5315,7 +5275,7 @@
         <v>1</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="1:10">
@@ -5328,19 +5288,19 @@
         <v>1</v>
       </c>
       <c r="E104" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F104" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="G104" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="F104" s="16" t="s">
+      <c r="H104" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="G104" s="16" t="s">
+      <c r="I104" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="H104" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="J104" s="1"/>
     </row>
@@ -5354,19 +5314,19 @@
         <v>1</v>
       </c>
       <c r="E105" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F105" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="G105" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="F105" s="16" t="s">
+      <c r="H105" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="G105" s="16" t="s">
+      <c r="I105" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="H105" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="J105" s="1"/>
     </row>
@@ -5380,19 +5340,19 @@
         <v>1</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F106" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="G106" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="F106" s="16" t="s">
+      <c r="H106" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="G106" s="16" t="s">
+      <c r="I106" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="H106" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="J106" s="1"/>
     </row>
@@ -5406,19 +5366,19 @@
         <v>1</v>
       </c>
       <c r="E107" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F107" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="G107" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="F107" s="16" t="s">
+      <c r="H107" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="G107" s="16" t="s">
+      <c r="I107" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="H107" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="J107" s="1"/>
     </row>
@@ -5432,19 +5392,19 @@
         <v>1</v>
       </c>
       <c r="E108" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F108" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="G108" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H108" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="F108" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="G108" s="16" t="s">
+      <c r="I108" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="H108" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="J108" s="1"/>
     </row>
@@ -5483,7 +5443,7 @@
     </row>
     <row r="115" customHeight="1" spans="7:8">
       <c r="G115" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H115" s="5"/>
     </row>
@@ -5615,19 +5575,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>192</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>194</v>
       </c>
       <c r="H6" s="1">
         <v>500</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5638,20 +5598,20 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7:H15" si="0">H6+500</f>
         <v>1000</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5662,20 +5622,20 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5686,20 +5646,20 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5710,20 +5670,20 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5734,20 +5694,20 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5758,20 +5718,20 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="0"/>
         <v>3500</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5782,20 +5742,20 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5806,20 +5766,20 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="0"/>
         <v>4500</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5830,20 +5790,20 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5854,20 +5814,20 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" ref="H16:H35" si="1">H15+5000</f>
         <v>10000</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -5878,20 +5838,20 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="1"/>
         <v>15000</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -5902,20 +5862,20 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="1"/>
         <v>20000</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -5926,20 +5886,20 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="1"/>
         <v>25000</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -5950,20 +5910,20 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -5974,20 +5934,20 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="1"/>
         <v>35000</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -5998,20 +5958,20 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6022,20 +5982,20 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6046,20 +6006,20 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" si="1"/>
         <v>50000</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6070,20 +6030,20 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" si="1"/>
         <v>55000</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6094,20 +6054,20 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" si="1"/>
         <v>60000</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6118,20 +6078,20 @@
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" si="1"/>
         <v>65000</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6142,20 +6102,20 @@
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" si="1"/>
         <v>70000</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6166,20 +6126,20 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H29" s="1">
         <f t="shared" si="1"/>
         <v>75000</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6190,20 +6150,20 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H30" s="1">
         <f t="shared" si="1"/>
         <v>80000</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6214,20 +6174,20 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" si="1"/>
         <v>85000</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6238,20 +6198,20 @@
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H32" s="1">
         <f t="shared" si="1"/>
         <v>90000</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6262,20 +6222,20 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H33" s="1">
         <f t="shared" si="1"/>
         <v>95000</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6286,20 +6246,20 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H34" s="1">
         <f t="shared" si="1"/>
         <v>100000</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6310,20 +6270,20 @@
         <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H35" s="1">
         <f t="shared" si="1"/>
         <v>105000</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106" customFormat="1" customHeight="1" spans="1:10">
@@ -6463,19 +6423,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>225</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>227</v>
       </c>
       <c r="H6" s="1">
         <v>100</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6486,20 +6446,20 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7:H70" si="0">H6+100</f>
         <v>200</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6510,20 +6470,20 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6534,20 +6494,20 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6558,20 +6518,20 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6582,20 +6542,20 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6606,20 +6566,20 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6630,20 +6590,20 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6654,20 +6614,20 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6678,20 +6638,20 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6702,20 +6662,20 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6726,20 +6686,20 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6750,20 +6710,20 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6774,20 +6734,20 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6798,20 +6758,20 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6822,20 +6782,20 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6846,20 +6806,20 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="0"/>
         <v>1700</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6870,20 +6830,20 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6894,20 +6854,20 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6918,20 +6878,20 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6942,20 +6902,20 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" si="0"/>
         <v>2100</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6966,20 +6926,20 @@
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6990,20 +6950,20 @@
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7014,20 +6974,20 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H29" s="1">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7038,20 +6998,20 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H30" s="1">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7062,20 +7022,20 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" si="0"/>
         <v>2600</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7086,20 +7046,20 @@
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H32" s="1">
         <f t="shared" si="0"/>
         <v>2700</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7110,20 +7070,20 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H33" s="1">
         <f t="shared" si="0"/>
         <v>2800</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7134,20 +7094,20 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H34" s="1">
         <f t="shared" si="0"/>
         <v>2900</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7158,20 +7118,20 @@
         <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H35" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7182,20 +7142,20 @@
         <v>1</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H36" s="1">
         <f t="shared" si="0"/>
         <v>3100</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7206,20 +7166,20 @@
         <v>1</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H37" s="1">
         <f t="shared" si="0"/>
         <v>3200</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7230,20 +7190,20 @@
         <v>1</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H38" s="1">
         <f t="shared" si="0"/>
         <v>3300</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:9">
@@ -7254,20 +7214,20 @@
         <v>1</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H39" s="1">
         <f t="shared" si="0"/>
         <v>3400</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:9">
@@ -7278,20 +7238,20 @@
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H40" s="1">
         <f t="shared" si="0"/>
         <v>3500</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:9">
@@ -7302,20 +7262,20 @@
         <v>1</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" si="0"/>
         <v>3600</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:9">
@@ -7326,20 +7286,20 @@
         <v>1</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H42" s="1">
         <f t="shared" si="0"/>
         <v>3700</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:9">
@@ -7350,20 +7310,20 @@
         <v>1</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H43" s="1">
         <f t="shared" si="0"/>
         <v>3800</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:9">
@@ -7374,20 +7334,20 @@
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H44" s="1">
         <f t="shared" si="0"/>
         <v>3900</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:9">
@@ -7398,20 +7358,20 @@
         <v>1</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H45" s="1">
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:9">
@@ -7422,20 +7382,20 @@
         <v>1</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H46" s="1">
         <f t="shared" si="0"/>
         <v>4100</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:9">
@@ -7446,20 +7406,20 @@
         <v>1</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H47" s="1">
         <f t="shared" si="0"/>
         <v>4200</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:9">
@@ -7470,20 +7430,20 @@
         <v>1</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H48" s="1">
         <f t="shared" si="0"/>
         <v>4300</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:9">
@@ -7494,20 +7454,20 @@
         <v>1</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H49" s="1">
         <f t="shared" si="0"/>
         <v>4400</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:9">
@@ -7518,20 +7478,20 @@
         <v>1</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H50" s="1">
         <f t="shared" si="0"/>
         <v>4500</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:9">
@@ -7542,20 +7502,20 @@
         <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H51" s="1">
         <f t="shared" si="0"/>
         <v>4600</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:9">
@@ -7566,20 +7526,20 @@
         <v>1</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H52" s="1">
         <f t="shared" si="0"/>
         <v>4700</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:9">
@@ -7590,20 +7550,20 @@
         <v>1</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H53" s="1">
         <f t="shared" si="0"/>
         <v>4800</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:9">
@@ -7614,20 +7574,20 @@
         <v>1</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H54" s="1">
         <f t="shared" si="0"/>
         <v>4900</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:9">
@@ -7638,20 +7598,20 @@
         <v>1</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H55" s="1">
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:9">
@@ -7662,20 +7622,20 @@
         <v>1</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H56" s="1">
         <f t="shared" si="0"/>
         <v>5100</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:9">
@@ -7686,20 +7646,20 @@
         <v>1</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H57" s="1">
         <f t="shared" si="0"/>
         <v>5200</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:9">
@@ -7710,20 +7670,20 @@
         <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H58" s="1">
         <f t="shared" si="0"/>
         <v>5300</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:9">
@@ -7734,20 +7694,20 @@
         <v>1</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H59" s="1">
         <f t="shared" si="0"/>
         <v>5400</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:9">
@@ -7758,20 +7718,20 @@
         <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H60" s="1">
         <f t="shared" si="0"/>
         <v>5500</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:9">
@@ -7782,20 +7742,20 @@
         <v>1</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H61" s="1">
         <f t="shared" si="0"/>
         <v>5600</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:9">
@@ -7806,20 +7766,20 @@
         <v>1</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H62" s="1">
         <f t="shared" si="0"/>
         <v>5700</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:9">
@@ -7830,20 +7790,20 @@
         <v>1</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H63" s="1">
         <f t="shared" si="0"/>
         <v>5800</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:9">
@@ -7854,20 +7814,20 @@
         <v>1</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H64" s="1">
         <f t="shared" si="0"/>
         <v>5900</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:9">
@@ -7878,20 +7838,20 @@
         <v>1</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H65" s="1">
         <f t="shared" si="0"/>
         <v>6000</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:9">
@@ -7902,20 +7862,20 @@
         <v>1</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H66" s="1">
         <f t="shared" si="0"/>
         <v>6100</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:9">
@@ -7926,20 +7886,20 @@
         <v>1</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H67" s="1">
         <f t="shared" si="0"/>
         <v>6200</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:9">
@@ -7950,20 +7910,20 @@
         <v>1</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H68" s="1">
         <f t="shared" si="0"/>
         <v>6300</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:9">
@@ -7974,20 +7934,20 @@
         <v>1</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F69" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H69" s="1">
         <f t="shared" si="0"/>
         <v>6400</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:9">
@@ -7998,20 +7958,20 @@
         <v>1</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="0"/>
         <v>6500</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:9">
@@ -8022,20 +7982,20 @@
         <v>1</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F71" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H71" s="1">
         <f t="shared" ref="H71:H105" si="1">H70+100</f>
         <v>6600</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:9">
@@ -8046,20 +8006,20 @@
         <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H72" s="1">
         <f t="shared" si="1"/>
         <v>6700</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:9">
@@ -8070,20 +8030,20 @@
         <v>1</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F73" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H73" s="1">
         <f t="shared" si="1"/>
         <v>6800</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:9">
@@ -8094,20 +8054,20 @@
         <v>1</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H74" s="1">
         <f t="shared" si="1"/>
         <v>6900</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:9">
@@ -8118,20 +8078,20 @@
         <v>1</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H75" s="1">
         <f t="shared" si="1"/>
         <v>7000</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:9">
@@ -8142,20 +8102,20 @@
         <v>1</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H76" s="1">
         <f t="shared" si="1"/>
         <v>7100</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:9">
@@ -8166,20 +8126,20 @@
         <v>1</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H77" s="1">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:9">
@@ -8190,20 +8150,20 @@
         <v>1</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H78" s="1">
         <f t="shared" si="1"/>
         <v>7300</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:9">
@@ -8214,20 +8174,20 @@
         <v>1</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F79" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H79" s="1">
         <f t="shared" si="1"/>
         <v>7400</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:9">
@@ -8238,20 +8198,20 @@
         <v>1</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F80" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H80" s="1">
         <f t="shared" si="1"/>
         <v>7500</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:9">
@@ -8262,20 +8222,20 @@
         <v>1</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F81" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H81" s="1">
         <f t="shared" si="1"/>
         <v>7600</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:9">
@@ -8286,20 +8246,20 @@
         <v>1</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F82" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H82" s="1">
         <f t="shared" si="1"/>
         <v>7700</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:9">
@@ -8310,20 +8270,20 @@
         <v>1</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F83" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H83" s="1">
         <f t="shared" si="1"/>
         <v>7800</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:9">
@@ -8334,20 +8294,20 @@
         <v>1</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H84" s="1">
         <f t="shared" si="1"/>
         <v>7900</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:9">
@@ -8358,20 +8318,20 @@
         <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H85" s="1">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:9">
@@ -8382,20 +8342,20 @@
         <v>1</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H86" s="1">
         <f t="shared" si="1"/>
         <v>8100</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:9">
@@ -8406,20 +8366,20 @@
         <v>1</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H87" s="1">
         <f t="shared" si="1"/>
         <v>8200</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:9">
@@ -8430,20 +8390,20 @@
         <v>1</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H88" s="1">
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:9">
@@ -8454,20 +8414,20 @@
         <v>1</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F89" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H89" s="1">
         <f t="shared" si="1"/>
         <v>8400</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:9">
@@ -8478,20 +8438,20 @@
         <v>1</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F90" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H90" s="1">
         <f t="shared" si="1"/>
         <v>8500</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:9">
@@ -8502,20 +8462,20 @@
         <v>1</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F91" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H91" s="1">
         <f t="shared" si="1"/>
         <v>8600</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:9">
@@ -8526,20 +8486,20 @@
         <v>1</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F92" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H92" s="1">
         <f t="shared" si="1"/>
         <v>8700</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:9">
@@ -8550,20 +8510,20 @@
         <v>1</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F93" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H93" s="1">
         <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:9">
@@ -8574,20 +8534,20 @@
         <v>1</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F94" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H94" s="1">
         <f t="shared" si="1"/>
         <v>8900</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:9">
@@ -8598,20 +8558,20 @@
         <v>1</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H95" s="1">
         <f t="shared" si="1"/>
         <v>9000</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:9">
@@ -8622,20 +8582,20 @@
         <v>1</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F96" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H96" s="1">
         <f t="shared" si="1"/>
         <v>9100</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:9">
@@ -8646,20 +8606,20 @@
         <v>1</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F97" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G97" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H97" s="1">
         <f t="shared" si="1"/>
         <v>9200</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:9">
@@ -8670,20 +8630,20 @@
         <v>1</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F98" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G98" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H98" s="1">
         <f t="shared" si="1"/>
         <v>9300</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:9">
@@ -8694,20 +8654,20 @@
         <v>1</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F99" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G99" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H99" s="1">
         <f t="shared" si="1"/>
         <v>9400</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:9">
@@ -8718,20 +8678,20 @@
         <v>1</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F100" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G100" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H100" s="1">
         <f t="shared" si="1"/>
         <v>9500</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:9">
@@ -8742,20 +8702,20 @@
         <v>1</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F101" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H101" s="1">
         <f t="shared" si="1"/>
         <v>9600</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:9">
@@ -8766,20 +8726,20 @@
         <v>1</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F102" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G102" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H102" s="1">
         <f t="shared" si="1"/>
         <v>9700</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:9">
@@ -8790,20 +8750,20 @@
         <v>1</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F103" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G103" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H103" s="1">
         <f t="shared" si="1"/>
         <v>9800</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:9">
@@ -8814,20 +8774,20 @@
         <v>1</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F104" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G104" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H104" s="1">
         <f t="shared" si="1"/>
         <v>9900</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:9">
@@ -8838,20 +8798,20 @@
         <v>1</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F105" s="16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G105" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H105" s="1">
         <f t="shared" si="1"/>
         <v>10000</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -8979,19 +8939,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H6" s="1">
         <v>200</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9002,20 +8962,20 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7:H25" si="0">H6+200</f>
         <v>400</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9026,20 +8986,20 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9050,20 +9010,20 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9074,20 +9034,20 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9098,20 +9058,20 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9122,20 +9082,20 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9146,20 +9106,20 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9170,20 +9130,20 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9194,20 +9154,20 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9218,20 +9178,20 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9242,20 +9202,20 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9266,20 +9226,20 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="0"/>
         <v>2600</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9290,20 +9250,20 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="0"/>
         <v>2800</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9314,20 +9274,20 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9338,20 +9298,20 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="0"/>
         <v>3200</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9362,20 +9322,20 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="0"/>
         <v>3400</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9386,20 +9346,20 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" si="0"/>
         <v>3600</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9410,20 +9370,20 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" si="0"/>
         <v>3800</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9434,20 +9394,20 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" customFormat="1" customHeight="1" spans="1:10">
@@ -9587,7 +9547,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
@@ -9599,7 +9559,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9610,7 +9570,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F7" s="1">
         <v>4</v>
@@ -9622,7 +9582,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9633,7 +9593,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F8" s="1">
         <v>4</v>
@@ -9645,7 +9605,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9656,7 +9616,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
@@ -9668,7 +9628,7 @@
         <v>4</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9679,7 +9639,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F10" s="1">
         <v>4</v>
@@ -9691,7 +9651,7 @@
         <v>5</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9702,7 +9662,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F11" s="1">
         <v>4</v>
@@ -9714,7 +9674,7 @@
         <v>6</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9725,7 +9685,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F12" s="1">
         <v>4</v>
@@ -9737,7 +9697,7 @@
         <v>7</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9748,7 +9708,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F13" s="1">
         <v>4</v>
@@ -9760,7 +9720,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9771,7 +9731,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F14" s="1">
         <v>4</v>
@@ -9783,7 +9743,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9794,7 +9754,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F15" s="1">
         <v>4</v>
@@ -9806,7 +9766,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9817,7 +9777,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F16" s="1">
         <v>4</v>
@@ -9829,7 +9789,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9840,7 +9800,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F17" s="1">
         <v>4</v>
@@ -9852,7 +9812,7 @@
         <v>2</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9863,7 +9823,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F18" s="1">
         <v>4</v>
@@ -9875,7 +9835,7 @@
         <v>3</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9886,7 +9846,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F19" s="1">
         <v>4</v>
@@ -9898,7 +9858,7 @@
         <v>4</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9909,7 +9869,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F20" s="1">
         <v>4</v>
@@ -9921,7 +9881,7 @@
         <v>5</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9932,7 +9892,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F21" s="1">
         <v>4</v>
@@ -9944,7 +9904,7 @@
         <v>6</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9955,7 +9915,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F22" s="1">
         <v>4</v>
@@ -9967,7 +9927,7 @@
         <v>7</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9978,7 +9938,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F23" s="1">
         <v>4</v>
@@ -9990,7 +9950,7 @@
         <v>8</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10001,7 +9961,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F24" s="1">
         <v>4</v>
@@ -10013,7 +9973,7 @@
         <v>9</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10024,7 +9984,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F25" s="1">
         <v>4</v>
@@ -10036,7 +9996,7 @@
         <v>10</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10047,7 +10007,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F26" s="1">
         <v>4</v>
@@ -10059,7 +10019,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10070,7 +10030,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F27" s="1">
         <v>4</v>
@@ -10082,7 +10042,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10093,7 +10053,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F28" s="1">
         <v>4</v>
@@ -10105,7 +10065,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10116,7 +10076,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F29" s="1">
         <v>4</v>
@@ -10128,7 +10088,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10139,7 +10099,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F30" s="1">
         <v>4</v>
@@ -10151,7 +10111,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10162,7 +10122,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F31" s="1">
         <v>4</v>
@@ -10174,7 +10134,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10185,7 +10145,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F32" s="1">
         <v>4</v>
@@ -10197,7 +10157,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10208,7 +10168,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F33" s="1">
         <v>4</v>
@@ -10220,7 +10180,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10231,7 +10191,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F34" s="1">
         <v>4</v>
@@ -10243,7 +10203,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10254,7 +10214,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F35" s="1">
         <v>4</v>
@@ -10266,7 +10226,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10277,7 +10237,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F37" s="1">
         <v>4</v>
@@ -10289,7 +10249,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10300,7 +10260,7 @@
         <v>1</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F38" s="1">
         <v>4</v>
@@ -10312,7 +10272,7 @@
         <v>2</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10323,7 +10283,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F39" s="1">
         <v>4</v>
@@ -10335,7 +10295,7 @@
         <v>3</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10346,7 +10306,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F40" s="1">
         <v>4</v>
@@ -10358,7 +10318,7 @@
         <v>4</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10369,7 +10329,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F41" s="1">
         <v>4</v>
@@ -10381,7 +10341,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10392,7 +10352,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F42" s="1">
         <v>4</v>
@@ -10404,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10415,7 +10375,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F43" s="1">
         <v>4</v>
@@ -10427,7 +10387,7 @@
         <v>1</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10438,7 +10398,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F44" s="1">
         <v>4</v>
@@ -10450,7 +10410,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10461,7 +10421,7 @@
         <v>1</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F45" s="1">
         <v>4</v>
@@ -10473,7 +10433,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10484,7 +10444,7 @@
         <v>1</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F46" s="1">
         <v>4</v>
@@ -10496,7 +10456,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:9">
@@ -10516,7 +10476,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F49" s="1">
         <v>4</v>
@@ -10528,7 +10488,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -10539,7 +10499,7 @@
         <v>1</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F50" s="1">
         <v>4</v>
@@ -10551,7 +10511,7 @@
         <v>2</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -10562,7 +10522,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F51" s="1">
         <v>4</v>
@@ -10574,7 +10534,7 @@
         <v>3</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -10585,7 +10545,7 @@
         <v>1</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F52" s="1">
         <v>4</v>
@@ -10597,7 +10557,7 @@
         <v>1</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -10608,7 +10568,7 @@
         <v>1</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F53" s="1">
         <v>4</v>
@@ -10620,7 +10580,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -10631,7 +10591,7 @@
         <v>1</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F54" s="1">
         <v>4</v>
@@ -10643,7 +10603,7 @@
         <v>1</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="1:10">
@@ -10775,7 +10735,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F6" s="2">
         <v>4</v>
@@ -10787,7 +10747,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10798,7 +10758,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F7" s="2">
         <v>4</v>
@@ -10810,7 +10770,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10821,7 +10781,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F8" s="2">
         <v>4</v>
@@ -10833,7 +10793,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10844,7 +10804,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F9" s="2">
         <v>4</v>
@@ -10856,7 +10816,7 @@
         <v>4</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10867,7 +10827,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F10" s="2">
         <v>4</v>
@@ -10879,7 +10839,7 @@
         <v>5</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10890,7 +10850,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F11" s="2">
         <v>4</v>
@@ -10902,7 +10862,7 @@
         <v>6</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10913,7 +10873,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F12" s="2">
         <v>4</v>
@@ -10925,7 +10885,7 @@
         <v>7</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10936,7 +10896,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F13" s="2">
         <v>4</v>
@@ -10948,7 +10908,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10959,7 +10919,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F14" s="2">
         <v>4</v>
@@ -10971,7 +10931,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10982,7 +10942,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F15" s="2">
         <v>4</v>
@@ -10994,7 +10954,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -11005,7 +10965,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F16" s="2">
         <v>4</v>
@@ -11017,7 +10977,7 @@
         <v>20</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11028,7 +10988,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F17" s="2">
         <v>4</v>
@@ -11040,7 +11000,7 @@
         <v>30</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11051,7 +11011,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F18" s="2">
         <v>4</v>
@@ -11063,7 +11023,7 @@
         <v>40</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11074,7 +11034,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F19" s="2">
         <v>4</v>
@@ -11086,7 +11046,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11097,7 +11057,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F20" s="2">
         <v>4</v>
@@ -11109,7 +11069,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11120,7 +11080,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F21" s="2">
         <v>4</v>
@@ -11132,7 +11092,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11143,7 +11103,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F22" s="2">
         <v>4</v>
@@ -11155,7 +11115,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11166,7 +11126,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F23" s="2">
         <v>4</v>
@@ -11178,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11194,7 +11154,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F25" s="2">
         <v>4</v>
@@ -11206,7 +11166,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11217,7 +11177,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F26" s="2">
         <v>4</v>
@@ -11229,7 +11189,7 @@
         <v>2</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11240,7 +11200,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F27" s="2">
         <v>4</v>
@@ -11252,7 +11212,7 @@
         <v>3</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11263,7 +11223,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F28" s="2">
         <v>4</v>
@@ -11275,7 +11235,7 @@
         <v>4</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11286,7 +11246,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F29" s="2">
         <v>4</v>
@@ -11298,7 +11258,7 @@
         <v>5</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11309,7 +11269,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F30" s="2">
         <v>4</v>
@@ -11321,7 +11281,7 @@
         <v>6</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11332,7 +11292,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F31" s="2">
         <v>4</v>
@@ -11344,7 +11304,7 @@
         <v>7</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11355,7 +11315,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F32" s="2">
         <v>4</v>
@@ -11367,7 +11327,7 @@
         <v>8</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" ht="18" customHeight="1" spans="1:11">
@@ -11378,7 +11338,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F33" s="2">
         <v>4</v>
@@ -11390,7 +11350,7 @@
         <v>9</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" ht="18" customHeight="1" spans="1:11">
@@ -11401,7 +11361,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F34" s="2">
         <v>4</v>
@@ -11413,7 +11373,7 @@
         <v>10</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" ht="18" customHeight="1" spans="1:11">
@@ -11491,19 +11451,19 @@
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G40" s="16" t="s">
         <v>429</v>
       </c>
-      <c r="F40" s="16" t="s">
+      <c r="H40" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="G40" s="16" t="s">
+      <c r="I40" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="H40" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="J40" s="1"/>
     </row>
@@ -11517,19 +11477,19 @@
         <v>1</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F41" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="H41" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="G41" s="16" t="s">
+      <c r="I41" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="H41" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="J41" s="1"/>
     </row>
@@ -11543,19 +11503,19 @@
         <v>1</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F42" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="H42" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="G42" s="16" t="s">
+      <c r="I42" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="H42" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="J42" s="1"/>
     </row>
@@ -11569,19 +11529,19 @@
         <v>1</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F43" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="H43" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="G43" s="16" t="s">
+      <c r="I43" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="H43" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="J43" s="1"/>
     </row>
@@ -11595,19 +11555,19 @@
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F44" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="H44" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="G44" s="16" t="s">
+      <c r="I44" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="H44" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="J44" s="1"/>
     </row>
@@ -11621,19 +11581,19 @@
         <v>1</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F45" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="H45" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="G45" s="16" t="s">
+      <c r="I45" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="H45" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="J45" s="1"/>
     </row>
@@ -11659,19 +11619,19 @@
         <v>1</v>
       </c>
       <c r="E47" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="H47" s="16" t="s">
         <v>439</v>
       </c>
-      <c r="F47" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="G47" s="16" t="s">
+      <c r="I47" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="H47" s="16" t="s">
-        <v>441</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>442</v>
       </c>
       <c r="J47" s="1"/>
     </row>
@@ -11685,19 +11645,19 @@
         <v>1</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G48" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="H48" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="H48" s="16" t="s">
-        <v>441</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>442</v>
       </c>
       <c r="J48" s="1"/>
     </row>
@@ -11709,19 +11669,19 @@
         <v>1</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G49" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="H49" s="16" t="s">
-        <v>441</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="50" spans="3:9">
@@ -11732,19 +11692,19 @@
         <v>1</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G50" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="H50" s="16" t="s">
-        <v>441</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="51" spans="3:9">
@@ -11755,19 +11715,19 @@
         <v>1</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G51" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="H51" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="I51" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="H51" s="16" t="s">
-        <v>441</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="52" spans="3:9">
@@ -11787,19 +11747,19 @@
         <v>1</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="H53" s="16" t="s">
         <v>447</v>
       </c>
-      <c r="F53" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="G53" s="16" t="s">
+      <c r="I53" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="H53" s="16" t="s">
-        <v>449</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="54" spans="3:9">
@@ -11810,19 +11770,19 @@
         <v>1</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G54" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="H54" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="I54" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="H54" s="16" t="s">
-        <v>449</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="55" spans="3:9">
@@ -11833,19 +11793,19 @@
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G55" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="H55" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="H55" s="16" t="s">
-        <v>449</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="56" spans="3:9">
@@ -11865,19 +11825,19 @@
         <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="H57" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="F57" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="G57" s="16" t="s">
+      <c r="I57" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="H57" s="16" t="s">
-        <v>455</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="58" spans="3:9">
@@ -11888,19 +11848,19 @@
         <v>1</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G58" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="H58" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="H58" s="16" t="s">
-        <v>455</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="59" spans="3:9">
@@ -11911,19 +11871,19 @@
         <v>1</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G59" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="H59" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="H59" s="16" t="s">
-        <v>455</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="60" spans="3:9">
@@ -11952,19 +11912,19 @@
         <v>1</v>
       </c>
       <c r="E62" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="F62" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="G62" s="16" t="s">
         <v>459</v>
       </c>
-      <c r="F62" s="16" t="s">
+      <c r="H62" s="16" t="s">
         <v>460</v>
       </c>
-      <c r="G62" s="16" t="s">
+      <c r="I62" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="H62" s="16" t="s">
-        <v>462</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="63" spans="3:9">
@@ -11975,19 +11935,19 @@
         <v>1</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G63" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="H63" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="H63" s="16" t="s">
-        <v>465</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="64" spans="3:9">
@@ -11998,19 +11958,19 @@
         <v>1</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G64" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="H64" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="H64" s="16" t="s">
-        <v>467</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -12021,19 +11981,19 @@
         <v>1</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G65" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="H65" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="H65" s="16" t="s">
-        <v>469</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -12044,19 +12004,19 @@
         <v>1</v>
       </c>
       <c r="E66" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F66" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="G66" s="16" t="s">
         <v>470</v>
       </c>
-      <c r="F66" s="16" t="s">
+      <c r="H66" s="16" t="s">
         <v>471</v>
       </c>
-      <c r="G66" s="16" t="s">
-        <v>472</v>
-      </c>
-      <c r="H66" s="16" t="s">
-        <v>473</v>
-      </c>
       <c r="I66" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -12067,19 +12027,19 @@
         <v>1</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="H67" s="16" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -12090,19 +12050,19 @@
         <v>1</v>
       </c>
       <c r="E70" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="G70" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="H70" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="G70" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="H70" s="18" t="s">
-        <v>432</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -12113,19 +12073,19 @@
         <v>1</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F71" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="G71" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="H71" s="18" t="s">
         <v>430</v>
       </c>
-      <c r="G71" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="H71" s="18" t="s">
-        <v>432</v>
-      </c>
       <c r="I71" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -12136,19 +12096,19 @@
         <v>1</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F72" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="G72" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="H72" s="18" t="s">
         <v>430</v>
       </c>
-      <c r="G72" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="H72" s="18" t="s">
-        <v>432</v>
-      </c>
       <c r="I72" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -12159,19 +12119,19 @@
         <v>1</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F73" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="G73" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="H73" s="18" t="s">
         <v>430</v>
       </c>
-      <c r="G73" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="H73" s="18" t="s">
-        <v>432</v>
-      </c>
       <c r="I73" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -12188,19 +12148,19 @@
         <v>1</v>
       </c>
       <c r="E75" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="F75" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G75" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="H75" s="16" t="s">
         <v>482</v>
       </c>
-      <c r="F75" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="G75" s="16" t="s">
+      <c r="I75" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="H75" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -12217,19 +12177,19 @@
         <v>1</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G76" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="H76" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="H76" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -12246,19 +12206,19 @@
         <v>1</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G77" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="H77" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="I77" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="H77" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -12275,19 +12235,19 @@
         <v>1</v>
       </c>
       <c r="E79" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F79" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G79" s="16" t="s">
+        <v>487</v>
+      </c>
+      <c r="H79" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="I79" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="F79" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="G79" s="16" t="s">
-        <v>489</v>
-      </c>
-      <c r="H79" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -12304,19 +12264,19 @@
         <v>1</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F80" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -12333,19 +12293,19 @@
         <v>1</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F81" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H81" s="16" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -12362,19 +12322,19 @@
         <v>1</v>
       </c>
       <c r="E83" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F83" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G83" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="H83" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="I83" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="F83" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="G83" s="16" t="s">
-        <v>494</v>
-      </c>
-      <c r="H83" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -12391,19 +12351,19 @@
         <v>1</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -12420,19 +12380,19 @@
         <v>1</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H85" s="16" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -12449,19 +12409,19 @@
         <v>1</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F86" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G86" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="H86" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="G86" s="16" t="s">
-        <v>494</v>
-      </c>
-      <c r="H86" s="16" t="s">
-        <v>432</v>
-      </c>
       <c r="I86" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="499">
   <si>
     <t>#</t>
   </si>
@@ -169,28 +169,28 @@
     <t>之后的及时删除</t>
   </si>
   <si>
-    <t>gx458</t>
+    <t>gx459</t>
   </si>
   <si>
     <t>4000,400,400</t>
   </si>
   <si>
-    <t>anyu458</t>
+    <t>anyu459</t>
   </si>
   <si>
     <t>20000,2000,1600</t>
   </si>
   <si>
-    <t>tt458</t>
+    <t>tt459</t>
   </si>
   <si>
     <t>9,5,9,4</t>
   </si>
   <si>
-    <t>4003,4004,4013,89</t>
-  </si>
-  <si>
-    <t>40000,4000,4000,12</t>
+    <t>4003,4004,4013,88</t>
+  </si>
+  <si>
+    <t>40000,4000,4000,6</t>
   </si>
   <si>
     <t>anyult23adu</t>
@@ -2926,12 +2926,6 @@
       <c r="H23" s="9"/>
     </row>
     <row r="24" customHeight="1" spans="1:9">
-      <c r="A24" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>0</v>
-      </c>
       <c r="C24" s="6">
         <v>99</v>
       </c>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="499">
   <si>
     <t>#</t>
   </si>
@@ -2926,6 +2926,12 @@
       <c r="H23" s="9"/>
     </row>
     <row r="24" customHeight="1" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>0</v>
+      </c>
       <c r="C24" s="6">
         <v>99</v>
       </c>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="501">
   <si>
     <t>#</t>
   </si>
@@ -181,6 +181,12 @@
     <t>20000,2000,1600</t>
   </si>
   <si>
+    <t>zq2026</t>
+  </si>
+  <si>
+    <t>10000,1000,800</t>
+  </si>
+  <si>
     <t>tt459</t>
   </si>
   <si>
@@ -193,7 +199,7 @@
     <t>40000,4000,4000,6</t>
   </si>
   <si>
-    <t>anyult23adu</t>
+    <t>anyult24kbc</t>
   </si>
   <si>
     <t>9,5,9,5,4,4,4,5</t>
@@ -202,10 +208,10 @@
     <t>4003,4004,4013,4008,22,26,28,4034</t>
   </si>
   <si>
-    <t>38888,3888,3888,688,20,12,12,20</t>
-  </si>
-  <si>
-    <t>副本券38888，Boss券3888，传世券3888，羽毛688，特戒20，神技12，魂骨12，时装精华20</t>
+    <t>38888,3888,3888,688,20,10,10,20</t>
+  </si>
+  <si>
+    <t>副本券38888，Boss券3888，传世券3888，羽毛688，特戒20，神技10，魂骨10，时装精华20</t>
   </si>
   <si>
     <t>anyult21acc</t>
@@ -2905,7 +2911,24 @@
       </c>
     </row>
     <row r="17" ht="17" customHeight="1" spans="1:9">
-      <c r="H17" s="9"/>
+      <c r="C17" s="6">
+        <v>43</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="18" ht="17" customHeight="1" spans="1:9">
       <c r="H18" s="9"/>
@@ -2939,16 +2962,16 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:9">
@@ -2970,19 +2993,19 @@
         <v>1</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:9">
@@ -2999,19 +3022,19 @@
         <v>1</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:9">
@@ -3257,19 +3280,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3280,19 +3303,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>52</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3303,19 +3326,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3326,19 +3349,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3349,19 +3372,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3372,19 +3395,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3399,7 +3422,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F13" s="1">
         <v>5</v>
@@ -3411,7 +3434,7 @@
         <v>600</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:19">
@@ -3422,7 +3445,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F14" s="1">
         <v>5</v>
@@ -3434,7 +3457,7 @@
         <v>1200</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:19">
@@ -3445,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F15" s="1">
         <v>5</v>
@@ -3457,7 +3480,7 @@
         <v>1800</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:19">
@@ -3468,7 +3491,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F16" s="1">
         <v>5</v>
@@ -3480,7 +3503,7 @@
         <v>2400</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:9">
@@ -3491,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F17" s="1">
         <v>5</v>
@@ -3503,7 +3526,7 @@
         <v>3000</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:9">
@@ -3514,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F19" s="1">
         <v>3</v>
@@ -3534,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F20" s="1">
         <v>3</v>
@@ -3554,7 +3577,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F21" s="1">
         <v>3</v>
@@ -3574,7 +3597,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F22" s="1">
         <v>5</v>
@@ -3586,7 +3609,7 @@
         <v>200000</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -3597,7 +3620,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F23" s="1">
         <v>4</v>
@@ -3606,7 +3629,7 @@
         <v>9</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:9">
@@ -3617,7 +3640,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F25" s="1">
         <v>18</v>
@@ -3629,7 +3652,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:9">
@@ -3640,7 +3663,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F26" s="1">
         <v>18</v>
@@ -3652,7 +3675,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:9">
@@ -3663,7 +3686,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F27" s="1">
         <v>18</v>
@@ -3675,7 +3698,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:9">
@@ -3686,7 +3709,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F28" s="1">
         <v>18</v>
@@ -3698,7 +3721,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:9">
@@ -3709,7 +3732,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F29" s="1">
         <v>18</v>
@@ -3721,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:9">
@@ -3732,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F30" s="1">
         <v>18</v>
@@ -3744,7 +3767,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:9">
@@ -3755,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F31" s="1">
         <v>18</v>
@@ -3767,7 +3790,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:9">
@@ -3778,7 +3801,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F32" s="1">
         <v>18</v>
@@ -3790,7 +3813,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:9">
@@ -3804,7 +3827,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F34" s="2">
         <v>4</v>
@@ -3816,7 +3839,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -3827,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F35" s="2">
         <v>4</v>
@@ -3839,7 +3862,7 @@
         <v>2</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -3850,7 +3873,7 @@
         <v>1</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F36" s="2">
         <v>4</v>
@@ -3862,7 +3885,7 @@
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -3873,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F37" s="2">
         <v>4</v>
@@ -3885,7 +3908,7 @@
         <v>4</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -3896,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F38" s="2">
         <v>4</v>
@@ -3908,7 +3931,7 @@
         <v>5</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -3919,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F39" s="2">
         <v>4</v>
@@ -3931,7 +3954,7 @@
         <v>6</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -3942,7 +3965,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F40" s="2">
         <v>4</v>
@@ -3954,7 +3977,7 @@
         <v>7</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:9">
@@ -3965,7 +3988,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F41" s="2">
         <v>4</v>
@@ -3977,7 +4000,7 @@
         <v>8</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:9">
@@ -3988,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F42" s="2">
         <v>4</v>
@@ -4000,7 +4023,7 @@
         <v>9</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:9">
@@ -4011,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F43" s="2">
         <v>4</v>
@@ -4023,7 +4046,7 @@
         <v>10</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:9">
@@ -4034,7 +4057,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F44" s="2">
         <v>4</v>
@@ -4046,7 +4069,7 @@
         <v>20</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:9">
@@ -4057,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F45" s="2">
         <v>4</v>
@@ -4069,7 +4092,7 @@
         <v>30</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:9">
@@ -4080,7 +4103,7 @@
         <v>1</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F46" s="2">
         <v>4</v>
@@ -4092,7 +4115,7 @@
         <v>40</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:9">
@@ -4112,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F48" s="1">
         <v>18</v>
@@ -4124,7 +4147,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:9">
@@ -4135,7 +4158,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F49" s="1">
         <v>18</v>
@@ -4147,7 +4170,7 @@
         <v>2</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:9">
@@ -4158,7 +4181,7 @@
         <v>1</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F50" s="1">
         <v>18</v>
@@ -4170,7 +4193,7 @@
         <v>3</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:9">
@@ -4181,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F51" s="1">
         <v>18</v>
@@ -4193,7 +4216,7 @@
         <v>4</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:9">
@@ -4204,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F52" s="1">
         <v>18</v>
@@ -4216,7 +4239,7 @@
         <v>5</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:9">
@@ -4227,7 +4250,7 @@
         <v>1</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F53" s="1">
         <v>18</v>
@@ -4239,7 +4262,7 @@
         <v>6</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:9">
@@ -4250,7 +4273,7 @@
         <v>1</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F54" s="1">
         <v>18</v>
@@ -4262,7 +4285,7 @@
         <v>7</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:9">
@@ -4273,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F55" s="1">
         <v>18</v>
@@ -4285,7 +4308,7 @@
         <v>8</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" customFormat="1" customHeight="1" spans="3:9">
@@ -4296,7 +4319,7 @@
         <v>1</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F56" s="1">
         <v>18</v>
@@ -4308,7 +4331,7 @@
         <v>9</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:9">
@@ -4319,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F57" s="1">
         <v>18</v>
@@ -4331,7 +4354,7 @@
         <v>10</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:9">
@@ -4342,7 +4365,7 @@
         <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F58" s="1">
         <v>18</v>
@@ -4354,7 +4377,7 @@
         <v>20</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:9">
@@ -4365,7 +4388,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F59" s="1">
         <v>18</v>
@@ -4377,7 +4400,7 @@
         <v>30</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:9">
@@ -4388,7 +4411,7 @@
         <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F60" s="1">
         <v>18</v>
@@ -4400,7 +4423,7 @@
         <v>40</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:9">
@@ -4429,7 +4452,7 @@
         <v>1</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F63" s="2">
         <v>4</v>
@@ -4441,7 +4464,7 @@
         <v>1</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:9">
@@ -4452,7 +4475,7 @@
         <v>1</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F64" s="2">
         <v>4</v>
@@ -4464,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:9">
@@ -4475,7 +4498,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F65" s="2">
         <v>4</v>
@@ -4487,7 +4510,7 @@
         <v>1</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:9">
@@ -4498,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F66" s="2">
         <v>4</v>
@@ -4510,7 +4533,7 @@
         <v>1</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:9">
@@ -4521,7 +4544,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F67" s="2">
         <v>4</v>
@@ -4533,7 +4556,7 @@
         <v>1</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:9">
@@ -4547,7 +4570,7 @@
         <v>1</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F69" s="1">
         <v>4</v>
@@ -4559,7 +4582,7 @@
         <v>1</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:9">
@@ -4570,7 +4593,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F70" s="1">
         <v>4</v>
@@ -4582,7 +4605,7 @@
         <v>2</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:9">
@@ -4593,7 +4616,7 @@
         <v>1</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F71" s="1">
         <v>4</v>
@@ -4605,7 +4628,7 @@
         <v>3</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:9">
@@ -4616,7 +4639,7 @@
         <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F72" s="1">
         <v>4</v>
@@ -4628,7 +4651,7 @@
         <v>4</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:9">
@@ -4639,7 +4662,7 @@
         <v>1</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F73" s="1">
         <v>4</v>
@@ -4651,7 +4674,7 @@
         <v>5</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:9">
@@ -4662,7 +4685,7 @@
         <v>1</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F74" s="1">
         <v>4</v>
@@ -4674,7 +4697,7 @@
         <v>6</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:9">
@@ -4685,7 +4708,7 @@
         <v>1</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F75" s="1">
         <v>4</v>
@@ -4697,7 +4720,7 @@
         <v>7</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:9">
@@ -4708,7 +4731,7 @@
         <v>1</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F76" s="1">
         <v>4</v>
@@ -4720,7 +4743,7 @@
         <v>8</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:9">
@@ -4731,7 +4754,7 @@
         <v>1</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F77" s="1">
         <v>4</v>
@@ -4743,7 +4766,7 @@
         <v>9</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:9">
@@ -4754,7 +4777,7 @@
         <v>1</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F78" s="1">
         <v>4</v>
@@ -4766,7 +4789,7 @@
         <v>10</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:9">
@@ -4777,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F79" s="1">
         <v>4</v>
@@ -4789,7 +4812,7 @@
         <v>10</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:9">
@@ -4800,7 +4823,7 @@
         <v>1</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F80" s="1">
         <v>4</v>
@@ -4812,7 +4835,7 @@
         <v>20</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:9">
@@ -4823,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F81" s="1">
         <v>4</v>
@@ -4835,7 +4858,7 @@
         <v>30</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:9">
@@ -4846,7 +4869,7 @@
         <v>1</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F82" s="1">
         <v>4</v>
@@ -4858,7 +4881,7 @@
         <v>10</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:9">
@@ -4869,7 +4892,7 @@
         <v>1</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F83" s="1">
         <v>4</v>
@@ -4881,7 +4904,7 @@
         <v>1</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:9">
@@ -4892,7 +4915,7 @@
         <v>1</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F84" s="1">
         <v>4</v>
@@ -4904,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:9">
@@ -4915,7 +4938,7 @@
         <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F85" s="1">
         <v>4</v>
@@ -4927,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:9">
@@ -4941,7 +4964,7 @@
         <v>1</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F87" s="1">
         <v>18</v>
@@ -4953,7 +4976,7 @@
         <v>1</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:9">
@@ -4964,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F88" s="1">
         <v>18</v>
@@ -4976,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:9">
@@ -4987,7 +5010,7 @@
         <v>1</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F89" s="1">
         <v>18</v>
@@ -4999,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:9">
@@ -5010,7 +5033,7 @@
         <v>1</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F90" s="1">
         <v>18</v>
@@ -5022,7 +5045,7 @@
         <v>1</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:9">
@@ -5033,7 +5056,7 @@
         <v>1</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F91" s="1">
         <v>18</v>
@@ -5045,7 +5068,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:9">
@@ -5056,7 +5079,7 @@
         <v>1</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F92" s="1">
         <v>18</v>
@@ -5068,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:9">
@@ -5079,7 +5102,7 @@
         <v>1</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F93" s="1">
         <v>18</v>
@@ -5091,7 +5114,7 @@
         <v>1</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:9">
@@ -5102,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F94" s="1">
         <v>18</v>
@@ -5114,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:9">
@@ -5125,7 +5148,7 @@
         <v>1</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F95" s="1">
         <v>18</v>
@@ -5137,7 +5160,7 @@
         <v>1</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:9">
@@ -5148,7 +5171,7 @@
         <v>1</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F96" s="1">
         <v>18</v>
@@ -5160,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:10">
@@ -5171,7 +5194,7 @@
         <v>1</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F97" s="1">
         <v>18</v>
@@ -5183,7 +5206,7 @@
         <v>1</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:10">
@@ -5194,7 +5217,7 @@
         <v>1</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F98" s="1">
         <v>18</v>
@@ -5206,7 +5229,7 @@
         <v>1</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:10">
@@ -5217,7 +5240,7 @@
         <v>1</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F99" s="1">
         <v>18</v>
@@ -5229,7 +5252,7 @@
         <v>1</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:10">
@@ -5240,7 +5263,7 @@
         <v>1</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F100" s="1">
         <v>18</v>
@@ -5252,7 +5275,7 @@
         <v>1</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:10">
@@ -5263,7 +5286,7 @@
         <v>1</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F101" s="1">
         <v>18</v>
@@ -5275,7 +5298,7 @@
         <v>1</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="1:10">
@@ -5288,19 +5311,19 @@
         <v>1</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F104" s="16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G104" s="16" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H104" s="17" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J104" s="1"/>
     </row>
@@ -5314,19 +5337,19 @@
         <v>1</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F105" s="16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G105" s="16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H105" s="17" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J105" s="1"/>
     </row>
@@ -5340,19 +5363,19 @@
         <v>1</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F106" s="16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G106" s="16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H106" s="17" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J106" s="1"/>
     </row>
@@ -5366,19 +5389,19 @@
         <v>1</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F107" s="16" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G107" s="16" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H107" s="17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J107" s="1"/>
     </row>
@@ -5392,19 +5415,19 @@
         <v>1</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F108" s="16" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H108" s="17" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J108" s="1"/>
     </row>
@@ -5443,7 +5466,7 @@
     </row>
     <row r="115" customHeight="1" spans="7:8">
       <c r="G115" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H115" s="5"/>
     </row>
@@ -5575,19 +5598,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H6" s="1">
         <v>500</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5598,20 +5621,20 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>194</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>192</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7:H15" si="0">H6+500</f>
         <v>1000</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5622,20 +5645,20 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5646,20 +5669,20 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5670,20 +5693,20 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5694,20 +5717,20 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5718,20 +5741,20 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="0"/>
         <v>3500</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5742,20 +5765,20 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5766,20 +5789,20 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="0"/>
         <v>4500</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5790,20 +5813,20 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -5814,20 +5837,20 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" ref="H16:H35" si="1">H15+5000</f>
         <v>10000</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -5838,20 +5861,20 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="1"/>
         <v>15000</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -5862,20 +5885,20 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="1"/>
         <v>20000</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -5886,20 +5909,20 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="1"/>
         <v>25000</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -5910,20 +5933,20 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -5934,20 +5957,20 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="1"/>
         <v>35000</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -5958,20 +5981,20 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -5982,20 +6005,20 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" si="1"/>
         <v>45000</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6006,20 +6029,20 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" si="1"/>
         <v>50000</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6030,20 +6053,20 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" si="1"/>
         <v>55000</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6054,20 +6077,20 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" si="1"/>
         <v>60000</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6078,20 +6101,20 @@
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" si="1"/>
         <v>65000</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6102,20 +6125,20 @@
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" si="1"/>
         <v>70000</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6126,20 +6149,20 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H29" s="1">
         <f t="shared" si="1"/>
         <v>75000</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6150,20 +6173,20 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H30" s="1">
         <f t="shared" si="1"/>
         <v>80000</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6174,20 +6197,20 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" si="1"/>
         <v>85000</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6198,20 +6221,20 @@
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H32" s="1">
         <f t="shared" si="1"/>
         <v>90000</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6222,20 +6245,20 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H33" s="1">
         <f t="shared" si="1"/>
         <v>95000</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6246,20 +6269,20 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H34" s="1">
         <f t="shared" si="1"/>
         <v>100000</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6270,20 +6293,20 @@
         <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H35" s="1">
         <f t="shared" si="1"/>
         <v>105000</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="106" customFormat="1" customHeight="1" spans="1:10">
@@ -6423,19 +6446,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H6" s="1">
         <v>100</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6446,20 +6469,20 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>225</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7:H70" si="0">H6+100</f>
         <v>200</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6470,20 +6493,20 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6494,20 +6517,20 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6518,20 +6541,20 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6542,20 +6565,20 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6566,20 +6589,20 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6590,20 +6613,20 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6614,20 +6637,20 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6638,20 +6661,20 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -6662,20 +6685,20 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6686,20 +6709,20 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6710,20 +6733,20 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6734,20 +6757,20 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6758,20 +6781,20 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6782,20 +6805,20 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6806,20 +6829,20 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="0"/>
         <v>1700</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6830,20 +6853,20 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6854,20 +6877,20 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6878,20 +6901,20 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6902,20 +6925,20 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" si="0"/>
         <v>2100</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6926,20 +6949,20 @@
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6950,20 +6973,20 @@
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6974,20 +6997,20 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H29" s="1">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -6998,20 +7021,20 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H30" s="1">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7022,20 +7045,20 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" si="0"/>
         <v>2600</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7046,20 +7069,20 @@
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H32" s="1">
         <f t="shared" si="0"/>
         <v>2700</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7070,20 +7093,20 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H33" s="1">
         <f t="shared" si="0"/>
         <v>2800</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7094,20 +7117,20 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H34" s="1">
         <f t="shared" si="0"/>
         <v>2900</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7118,20 +7141,20 @@
         <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H35" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7142,20 +7165,20 @@
         <v>1</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H36" s="1">
         <f t="shared" si="0"/>
         <v>3100</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7166,20 +7189,20 @@
         <v>1</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H37" s="1">
         <f t="shared" si="0"/>
         <v>3200</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -7190,20 +7213,20 @@
         <v>1</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H38" s="1">
         <f t="shared" si="0"/>
         <v>3300</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:9">
@@ -7214,20 +7237,20 @@
         <v>1</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H39" s="1">
         <f t="shared" si="0"/>
         <v>3400</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:9">
@@ -7238,20 +7261,20 @@
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H40" s="1">
         <f t="shared" si="0"/>
         <v>3500</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:9">
@@ -7262,20 +7285,20 @@
         <v>1</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" si="0"/>
         <v>3600</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:9">
@@ -7286,20 +7309,20 @@
         <v>1</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H42" s="1">
         <f t="shared" si="0"/>
         <v>3700</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:9">
@@ -7310,20 +7333,20 @@
         <v>1</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H43" s="1">
         <f t="shared" si="0"/>
         <v>3800</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:9">
@@ -7334,20 +7357,20 @@
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H44" s="1">
         <f t="shared" si="0"/>
         <v>3900</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:9">
@@ -7358,20 +7381,20 @@
         <v>1</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H45" s="1">
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:9">
@@ -7382,20 +7405,20 @@
         <v>1</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H46" s="1">
         <f t="shared" si="0"/>
         <v>4100</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:9">
@@ -7406,20 +7429,20 @@
         <v>1</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H47" s="1">
         <f t="shared" si="0"/>
         <v>4200</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:9">
@@ -7430,20 +7453,20 @@
         <v>1</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H48" s="1">
         <f t="shared" si="0"/>
         <v>4300</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:9">
@@ -7454,20 +7477,20 @@
         <v>1</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H49" s="1">
         <f t="shared" si="0"/>
         <v>4400</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:9">
@@ -7478,20 +7501,20 @@
         <v>1</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H50" s="1">
         <f t="shared" si="0"/>
         <v>4500</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:9">
@@ -7502,20 +7525,20 @@
         <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H51" s="1">
         <f t="shared" si="0"/>
         <v>4600</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:9">
@@ -7526,20 +7549,20 @@
         <v>1</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H52" s="1">
         <f t="shared" si="0"/>
         <v>4700</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:9">
@@ -7550,20 +7573,20 @@
         <v>1</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H53" s="1">
         <f t="shared" si="0"/>
         <v>4800</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:9">
@@ -7574,20 +7597,20 @@
         <v>1</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H54" s="1">
         <f t="shared" si="0"/>
         <v>4900</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:9">
@@ -7598,20 +7621,20 @@
         <v>1</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H55" s="1">
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:9">
@@ -7622,20 +7645,20 @@
         <v>1</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H56" s="1">
         <f t="shared" si="0"/>
         <v>5100</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:9">
@@ -7646,20 +7669,20 @@
         <v>1</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H57" s="1">
         <f t="shared" si="0"/>
         <v>5200</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:9">
@@ -7670,20 +7693,20 @@
         <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H58" s="1">
         <f t="shared" si="0"/>
         <v>5300</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:9">
@@ -7694,20 +7717,20 @@
         <v>1</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H59" s="1">
         <f t="shared" si="0"/>
         <v>5400</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:9">
@@ -7718,20 +7741,20 @@
         <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H60" s="1">
         <f t="shared" si="0"/>
         <v>5500</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:9">
@@ -7742,20 +7765,20 @@
         <v>1</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H61" s="1">
         <f t="shared" si="0"/>
         <v>5600</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:9">
@@ -7766,20 +7789,20 @@
         <v>1</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H62" s="1">
         <f t="shared" si="0"/>
         <v>5700</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:9">
@@ -7790,20 +7813,20 @@
         <v>1</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H63" s="1">
         <f t="shared" si="0"/>
         <v>5800</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:9">
@@ -7814,20 +7837,20 @@
         <v>1</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H64" s="1">
         <f t="shared" si="0"/>
         <v>5900</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:9">
@@ -7838,20 +7861,20 @@
         <v>1</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H65" s="1">
         <f t="shared" si="0"/>
         <v>6000</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:9">
@@ -7862,20 +7885,20 @@
         <v>1</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H66" s="1">
         <f t="shared" si="0"/>
         <v>6100</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:9">
@@ -7886,20 +7909,20 @@
         <v>1</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H67" s="1">
         <f t="shared" si="0"/>
         <v>6200</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:9">
@@ -7910,20 +7933,20 @@
         <v>1</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H68" s="1">
         <f t="shared" si="0"/>
         <v>6300</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:9">
@@ -7934,20 +7957,20 @@
         <v>1</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F69" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H69" s="1">
         <f t="shared" si="0"/>
         <v>6400</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:9">
@@ -7958,20 +7981,20 @@
         <v>1</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="0"/>
         <v>6500</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:9">
@@ -7982,20 +8005,20 @@
         <v>1</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F71" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H71" s="1">
         <f t="shared" ref="H71:H105" si="1">H70+100</f>
         <v>6600</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:9">
@@ -8006,20 +8029,20 @@
         <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H72" s="1">
         <f t="shared" si="1"/>
         <v>6700</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:9">
@@ -8030,20 +8053,20 @@
         <v>1</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F73" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H73" s="1">
         <f t="shared" si="1"/>
         <v>6800</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:9">
@@ -8054,20 +8077,20 @@
         <v>1</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H74" s="1">
         <f t="shared" si="1"/>
         <v>6900</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:9">
@@ -8078,20 +8101,20 @@
         <v>1</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H75" s="1">
         <f t="shared" si="1"/>
         <v>7000</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:9">
@@ -8102,20 +8125,20 @@
         <v>1</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H76" s="1">
         <f t="shared" si="1"/>
         <v>7100</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:9">
@@ -8126,20 +8149,20 @@
         <v>1</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H77" s="1">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:9">
@@ -8150,20 +8173,20 @@
         <v>1</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H78" s="1">
         <f t="shared" si="1"/>
         <v>7300</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:9">
@@ -8174,20 +8197,20 @@
         <v>1</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F79" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H79" s="1">
         <f t="shared" si="1"/>
         <v>7400</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:9">
@@ -8198,20 +8221,20 @@
         <v>1</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F80" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H80" s="1">
         <f t="shared" si="1"/>
         <v>7500</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:9">
@@ -8222,20 +8245,20 @@
         <v>1</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F81" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H81" s="1">
         <f t="shared" si="1"/>
         <v>7600</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:9">
@@ -8246,20 +8269,20 @@
         <v>1</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F82" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H82" s="1">
         <f t="shared" si="1"/>
         <v>7700</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:9">
@@ -8270,20 +8293,20 @@
         <v>1</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F83" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H83" s="1">
         <f t="shared" si="1"/>
         <v>7800</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:9">
@@ -8294,20 +8317,20 @@
         <v>1</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H84" s="1">
         <f t="shared" si="1"/>
         <v>7900</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:9">
@@ -8318,20 +8341,20 @@
         <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H85" s="1">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:9">
@@ -8342,20 +8365,20 @@
         <v>1</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H86" s="1">
         <f t="shared" si="1"/>
         <v>8100</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:9">
@@ -8366,20 +8389,20 @@
         <v>1</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H87" s="1">
         <f t="shared" si="1"/>
         <v>8200</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:9">
@@ -8390,20 +8413,20 @@
         <v>1</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H88" s="1">
         <f t="shared" si="1"/>
         <v>8300</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:9">
@@ -8414,20 +8437,20 @@
         <v>1</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F89" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H89" s="1">
         <f t="shared" si="1"/>
         <v>8400</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:9">
@@ -8438,20 +8461,20 @@
         <v>1</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F90" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H90" s="1">
         <f t="shared" si="1"/>
         <v>8500</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:9">
@@ -8462,20 +8485,20 @@
         <v>1</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F91" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H91" s="1">
         <f t="shared" si="1"/>
         <v>8600</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:9">
@@ -8486,20 +8509,20 @@
         <v>1</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F92" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H92" s="1">
         <f t="shared" si="1"/>
         <v>8700</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:9">
@@ -8510,20 +8533,20 @@
         <v>1</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F93" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H93" s="1">
         <f t="shared" si="1"/>
         <v>8800</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:9">
@@ -8534,20 +8557,20 @@
         <v>1</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F94" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H94" s="1">
         <f t="shared" si="1"/>
         <v>8900</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:9">
@@ -8558,20 +8581,20 @@
         <v>1</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H95" s="1">
         <f t="shared" si="1"/>
         <v>9000</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:9">
@@ -8582,20 +8605,20 @@
         <v>1</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F96" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H96" s="1">
         <f t="shared" si="1"/>
         <v>9100</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:9">
@@ -8606,20 +8629,20 @@
         <v>1</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F97" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G97" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H97" s="1">
         <f t="shared" si="1"/>
         <v>9200</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:9">
@@ -8630,20 +8653,20 @@
         <v>1</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F98" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G98" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H98" s="1">
         <f t="shared" si="1"/>
         <v>9300</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:9">
@@ -8654,20 +8677,20 @@
         <v>1</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F99" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G99" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H99" s="1">
         <f t="shared" si="1"/>
         <v>9400</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:9">
@@ -8678,20 +8701,20 @@
         <v>1</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F100" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G100" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H100" s="1">
         <f t="shared" si="1"/>
         <v>9500</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:9">
@@ -8702,20 +8725,20 @@
         <v>1</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F101" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H101" s="1">
         <f t="shared" si="1"/>
         <v>9600</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:9">
@@ -8726,20 +8749,20 @@
         <v>1</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F102" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G102" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H102" s="1">
         <f t="shared" si="1"/>
         <v>9700</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:9">
@@ -8750,20 +8773,20 @@
         <v>1</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F103" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G103" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H103" s="1">
         <f t="shared" si="1"/>
         <v>9800</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:9">
@@ -8774,20 +8797,20 @@
         <v>1</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F104" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G104" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H104" s="1">
         <f t="shared" si="1"/>
         <v>9900</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:9">
@@ -8798,20 +8821,20 @@
         <v>1</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F105" s="16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G105" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H105" s="1">
         <f t="shared" si="1"/>
         <v>10000</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -8939,19 +8962,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H6" s="1">
         <v>200</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -8962,20 +8985,20 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>329</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>327</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" ref="H7:H25" si="0">H6+200</f>
         <v>400</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -8986,20 +9009,20 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9010,20 +9033,20 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9034,20 +9057,20 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9058,20 +9081,20 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9082,20 +9105,20 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9106,20 +9129,20 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9130,20 +9153,20 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9154,20 +9177,20 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9178,20 +9201,20 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9202,20 +9225,20 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9226,20 +9249,20 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="0"/>
         <v>2600</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9250,20 +9273,20 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="0"/>
         <v>2800</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9274,20 +9297,20 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9298,20 +9321,20 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="0"/>
         <v>3200</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9322,20 +9345,20 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="0"/>
         <v>3400</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9346,20 +9369,20 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" si="0"/>
         <v>3600</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9370,20 +9393,20 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" si="0"/>
         <v>3800</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -9394,20 +9417,20 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" customFormat="1" customHeight="1" spans="1:10">
@@ -9547,7 +9570,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
@@ -9559,7 +9582,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9570,7 +9593,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F7" s="1">
         <v>4</v>
@@ -9582,7 +9605,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9593,7 +9616,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F8" s="1">
         <v>4</v>
@@ -9605,7 +9628,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9616,7 +9639,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
@@ -9628,7 +9651,7 @@
         <v>4</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9639,7 +9662,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F10" s="1">
         <v>4</v>
@@ -9651,7 +9674,7 @@
         <v>5</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9662,7 +9685,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F11" s="1">
         <v>4</v>
@@ -9674,7 +9697,7 @@
         <v>6</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9685,7 +9708,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F12" s="1">
         <v>4</v>
@@ -9697,7 +9720,7 @@
         <v>7</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9708,7 +9731,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F13" s="1">
         <v>4</v>
@@ -9720,7 +9743,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9731,7 +9754,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F14" s="1">
         <v>4</v>
@@ -9743,7 +9766,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9754,7 +9777,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F15" s="1">
         <v>4</v>
@@ -9766,7 +9789,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -9777,7 +9800,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F16" s="1">
         <v>4</v>
@@ -9789,7 +9812,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9800,7 +9823,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F17" s="1">
         <v>4</v>
@@ -9812,7 +9835,7 @@
         <v>2</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9823,7 +9846,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F18" s="1">
         <v>4</v>
@@ -9835,7 +9858,7 @@
         <v>3</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9846,7 +9869,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F19" s="1">
         <v>4</v>
@@ -9858,7 +9881,7 @@
         <v>4</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9869,7 +9892,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F20" s="1">
         <v>4</v>
@@ -9881,7 +9904,7 @@
         <v>5</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9892,7 +9915,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F21" s="1">
         <v>4</v>
@@ -9904,7 +9927,7 @@
         <v>6</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9915,7 +9938,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F22" s="1">
         <v>4</v>
@@ -9927,7 +9950,7 @@
         <v>7</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9938,7 +9961,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F23" s="1">
         <v>4</v>
@@ -9950,7 +9973,7 @@
         <v>8</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9961,7 +9984,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F24" s="1">
         <v>4</v>
@@ -9973,7 +9996,7 @@
         <v>9</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -9984,7 +10007,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F25" s="1">
         <v>4</v>
@@ -9996,7 +10019,7 @@
         <v>10</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10007,7 +10030,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F26" s="1">
         <v>4</v>
@@ -10019,7 +10042,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10030,7 +10053,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F27" s="1">
         <v>4</v>
@@ -10042,7 +10065,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10053,7 +10076,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F28" s="1">
         <v>4</v>
@@ -10065,7 +10088,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10076,7 +10099,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F29" s="1">
         <v>4</v>
@@ -10088,7 +10111,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10099,7 +10122,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F30" s="1">
         <v>4</v>
@@ -10111,7 +10134,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10122,7 +10145,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F31" s="1">
         <v>4</v>
@@ -10134,7 +10157,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10145,7 +10168,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F32" s="1">
         <v>4</v>
@@ -10157,7 +10180,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10168,7 +10191,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F33" s="1">
         <v>4</v>
@@ -10180,7 +10203,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10191,7 +10214,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F34" s="1">
         <v>4</v>
@@ -10203,7 +10226,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10214,7 +10237,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F35" s="1">
         <v>4</v>
@@ -10226,7 +10249,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10237,7 +10260,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F37" s="1">
         <v>4</v>
@@ -10249,7 +10272,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10260,7 +10283,7 @@
         <v>1</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F38" s="1">
         <v>4</v>
@@ -10272,7 +10295,7 @@
         <v>2</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10283,7 +10306,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F39" s="1">
         <v>4</v>
@@ -10295,7 +10318,7 @@
         <v>3</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10306,7 +10329,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F40" s="1">
         <v>4</v>
@@ -10318,7 +10341,7 @@
         <v>4</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10329,7 +10352,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F41" s="1">
         <v>4</v>
@@ -10341,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10352,7 +10375,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F42" s="1">
         <v>4</v>
@@ -10364,7 +10387,7 @@
         <v>1</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10375,7 +10398,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F43" s="1">
         <v>4</v>
@@ -10387,7 +10410,7 @@
         <v>1</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10398,7 +10421,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F44" s="1">
         <v>4</v>
@@ -10410,7 +10433,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10421,7 +10444,7 @@
         <v>1</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F45" s="1">
         <v>4</v>
@@ -10433,7 +10456,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -10444,7 +10467,7 @@
         <v>1</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F46" s="1">
         <v>4</v>
@@ -10456,7 +10479,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:9">
@@ -10476,7 +10499,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F49" s="1">
         <v>4</v>
@@ -10488,7 +10511,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -10499,7 +10522,7 @@
         <v>1</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F50" s="1">
         <v>4</v>
@@ -10511,7 +10534,7 @@
         <v>2</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -10522,7 +10545,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F51" s="1">
         <v>4</v>
@@ -10534,7 +10557,7 @@
         <v>3</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -10545,7 +10568,7 @@
         <v>1</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F52" s="1">
         <v>4</v>
@@ -10557,7 +10580,7 @@
         <v>1</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -10568,7 +10591,7 @@
         <v>1</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F53" s="1">
         <v>4</v>
@@ -10580,7 +10603,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -10591,7 +10614,7 @@
         <v>1</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F54" s="1">
         <v>4</v>
@@ -10603,7 +10626,7 @@
         <v>1</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="1:10">
@@ -10735,7 +10758,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F6" s="2">
         <v>4</v>
@@ -10747,7 +10770,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10758,7 +10781,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F7" s="2">
         <v>4</v>
@@ -10770,7 +10793,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10781,7 +10804,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F8" s="2">
         <v>4</v>
@@ -10793,7 +10816,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10804,7 +10827,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F9" s="2">
         <v>4</v>
@@ -10816,7 +10839,7 @@
         <v>4</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10827,7 +10850,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F10" s="2">
         <v>4</v>
@@ -10839,7 +10862,7 @@
         <v>5</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10850,7 +10873,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F11" s="2">
         <v>4</v>
@@ -10862,7 +10885,7 @@
         <v>6</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10873,7 +10896,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F12" s="2">
         <v>4</v>
@@ -10885,7 +10908,7 @@
         <v>7</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10896,7 +10919,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F13" s="2">
         <v>4</v>
@@ -10908,7 +10931,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10919,7 +10942,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F14" s="2">
         <v>4</v>
@@ -10931,7 +10954,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10942,7 +10965,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F15" s="2">
         <v>4</v>
@@ -10954,7 +10977,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -10965,7 +10988,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F16" s="2">
         <v>4</v>
@@ -10977,7 +11000,7 @@
         <v>20</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -10988,7 +11011,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F17" s="2">
         <v>4</v>
@@ -11000,7 +11023,7 @@
         <v>30</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11011,7 +11034,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F18" s="2">
         <v>4</v>
@@ -11023,7 +11046,7 @@
         <v>40</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11034,7 +11057,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F19" s="2">
         <v>4</v>
@@ -11046,7 +11069,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11057,7 +11080,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F20" s="2">
         <v>4</v>
@@ -11069,7 +11092,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11080,7 +11103,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F21" s="2">
         <v>4</v>
@@ -11092,7 +11115,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11103,7 +11126,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F22" s="2">
         <v>4</v>
@@ -11115,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11126,7 +11149,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F23" s="2">
         <v>4</v>
@@ -11138,7 +11161,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11154,7 +11177,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F25" s="2">
         <v>4</v>
@@ -11166,7 +11189,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11177,7 +11200,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F26" s="2">
         <v>4</v>
@@ -11189,7 +11212,7 @@
         <v>2</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11200,7 +11223,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F27" s="2">
         <v>4</v>
@@ -11212,7 +11235,7 @@
         <v>3</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11223,7 +11246,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F28" s="2">
         <v>4</v>
@@ -11235,7 +11258,7 @@
         <v>4</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11246,7 +11269,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F29" s="2">
         <v>4</v>
@@ -11258,7 +11281,7 @@
         <v>5</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11269,7 +11292,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F30" s="2">
         <v>4</v>
@@ -11281,7 +11304,7 @@
         <v>6</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11292,7 +11315,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F31" s="2">
         <v>4</v>
@@ -11304,7 +11327,7 @@
         <v>7</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" ht="18" customHeight="1" spans="3:9">
@@ -11315,7 +11338,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F32" s="2">
         <v>4</v>
@@ -11327,7 +11350,7 @@
         <v>8</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" ht="18" customHeight="1" spans="1:11">
@@ -11338,7 +11361,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F33" s="2">
         <v>4</v>
@@ -11350,7 +11373,7 @@
         <v>9</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" ht="18" customHeight="1" spans="1:11">
@@ -11361,7 +11384,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F34" s="2">
         <v>4</v>
@@ -11373,7 +11396,7 @@
         <v>10</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" ht="18" customHeight="1" spans="1:11">
@@ -11451,19 +11474,19 @@
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J40" s="1"/>
     </row>
@@ -11477,19 +11500,19 @@
         <v>1</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="H41" s="16" t="s">
         <v>432</v>
       </c>
-      <c r="F41" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="G41" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="H41" s="16" t="s">
-        <v>430</v>
-      </c>
       <c r="I41" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J41" s="1"/>
     </row>
@@ -11503,19 +11526,19 @@
         <v>1</v>
       </c>
       <c r="E42" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="F42" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="G42" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="H42" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="J42" s="1"/>
     </row>
@@ -11529,19 +11552,19 @@
         <v>1</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J43" s="1"/>
     </row>
@@ -11555,19 +11578,19 @@
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J44" s="1"/>
     </row>
@@ -11581,19 +11604,19 @@
         <v>1</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J45" s="1"/>
     </row>
@@ -11619,19 +11642,19 @@
         <v>1</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J47" s="1"/>
     </row>
@@ -11645,19 +11668,19 @@
         <v>1</v>
       </c>
       <c r="E48" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="H48" s="16" t="s">
         <v>441</v>
       </c>
-      <c r="F48" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="G48" s="16" t="s">
-        <v>438</v>
-      </c>
-      <c r="H48" s="16" t="s">
-        <v>439</v>
-      </c>
       <c r="I48" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J48" s="1"/>
     </row>
@@ -11669,19 +11692,19 @@
         <v>1</v>
       </c>
       <c r="E49" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="F49" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="G49" s="16" t="s">
-        <v>438</v>
-      </c>
-      <c r="H49" s="16" t="s">
-        <v>439</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="50" spans="3:9">
@@ -11692,19 +11715,19 @@
         <v>1</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="51" spans="3:9">
@@ -11715,19 +11738,19 @@
         <v>1</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="52" spans="3:9">
@@ -11747,19 +11770,19 @@
         <v>1</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="54" spans="3:9">
@@ -11770,19 +11793,19 @@
         <v>1</v>
       </c>
       <c r="E54" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="H54" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="F54" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>446</v>
-      </c>
-      <c r="H54" s="16" t="s">
-        <v>447</v>
-      </c>
       <c r="I54" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="55" spans="3:9">
@@ -11793,19 +11816,19 @@
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="H55" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="F55" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="G55" s="16" t="s">
-        <v>446</v>
-      </c>
-      <c r="H55" s="16" t="s">
-        <v>447</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="56" spans="3:9">
@@ -11825,19 +11848,19 @@
         <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="58" spans="3:9">
@@ -11848,19 +11871,19 @@
         <v>1</v>
       </c>
       <c r="E58" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="H58" s="16" t="s">
         <v>455</v>
       </c>
-      <c r="F58" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="G58" s="16" t="s">
-        <v>452</v>
-      </c>
-      <c r="H58" s="16" t="s">
-        <v>453</v>
-      </c>
       <c r="I58" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="59" spans="3:9">
@@ -11871,19 +11894,19 @@
         <v>1</v>
       </c>
       <c r="E59" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="H59" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="F59" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="G59" s="16" t="s">
-        <v>452</v>
-      </c>
-      <c r="H59" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="60" spans="3:9">
@@ -11912,19 +11935,19 @@
         <v>1</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H62" s="16" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="63" spans="3:9">
@@ -11935,19 +11958,19 @@
         <v>1</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H63" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="64" spans="3:9">
@@ -11958,19 +11981,19 @@
         <v>1</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -11981,19 +12004,19 @@
         <v>1</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H65" s="16" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -12004,19 +12027,19 @@
         <v>1</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -12027,19 +12050,19 @@
         <v>1</v>
       </c>
       <c r="E67" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F67" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="G67" s="16" t="s">
         <v>472</v>
       </c>
-      <c r="F67" s="16" t="s">
-        <v>469</v>
-      </c>
-      <c r="G67" s="16" t="s">
-        <v>470</v>
-      </c>
       <c r="H67" s="16" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -12050,19 +12073,19 @@
         <v>1</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G70" s="18" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -12073,19 +12096,19 @@
         <v>1</v>
       </c>
       <c r="E71" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="G71" s="18" t="s">
         <v>477</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="G71" s="18" t="s">
-        <v>475</v>
-      </c>
       <c r="H71" s="18" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -12096,19 +12119,19 @@
         <v>1</v>
       </c>
       <c r="E72" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="G72" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="H72" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="G72" s="18" t="s">
-        <v>475</v>
-      </c>
-      <c r="H72" s="18" t="s">
-        <v>430</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -12119,19 +12142,19 @@
         <v>1</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G73" s="18" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="H73" s="18" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -12148,19 +12171,19 @@
         <v>1</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -12177,19 +12200,19 @@
         <v>1</v>
       </c>
       <c r="E76" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F76" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="G76" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="H76" s="16" t="s">
         <v>484</v>
       </c>
-      <c r="F76" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="G76" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="H76" s="16" t="s">
-        <v>482</v>
-      </c>
       <c r="I76" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -12206,19 +12229,19 @@
         <v>1</v>
       </c>
       <c r="E77" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="F77" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="G77" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="H77" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="I77" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="F77" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="G77" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="H77" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -12235,19 +12258,19 @@
         <v>1</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F79" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="H79" s="16" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -12264,19 +12287,19 @@
         <v>1</v>
       </c>
       <c r="E80" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="G80" s="16" t="s">
         <v>489</v>
       </c>
-      <c r="F80" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="G80" s="16" t="s">
-        <v>487</v>
-      </c>
       <c r="H80" s="16" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -12293,19 +12316,19 @@
         <v>1</v>
       </c>
       <c r="E81" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="G81" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="H81" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="I81" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="F81" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="G81" s="16" t="s">
-        <v>487</v>
-      </c>
-      <c r="H81" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -12322,19 +12345,19 @@
         <v>1</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F83" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -12351,19 +12374,19 @@
         <v>1</v>
       </c>
       <c r="E84" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="F84" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="G84" s="16" t="s">
         <v>494</v>
       </c>
-      <c r="F84" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="G84" s="16" t="s">
-        <v>492</v>
-      </c>
       <c r="H84" s="16" t="s">
+        <v>497</v>
+      </c>
+      <c r="I84" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -12380,19 +12403,19 @@
         <v>1</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="H85" s="16" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -12409,19 +12432,19 @@
         <v>1</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -169,19 +169,19 @@
     <t>之后的及时删除</t>
   </si>
   <si>
-    <t>gx459</t>
+    <t>gx460</t>
   </si>
   <si>
     <t>4000,400,400</t>
   </si>
   <si>
-    <t>anyu459</t>
+    <t>anyu460</t>
   </si>
   <si>
     <t>20000,2000,1600</t>
   </si>
   <si>
-    <t>zq2026</t>
+    <t>1012026</t>
   </si>
   <si>
     <t>10000,1000,800</t>
@@ -2917,7 +2917,7 @@
       <c r="D17" s="6">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="14" t="s">
         <v>35</v>
       </c>
       <c r="F17" s="14" t="s">

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -169,13 +169,13 @@
     <t>之后的及时删除</t>
   </si>
   <si>
-    <t>gx460</t>
+    <t>gx461</t>
   </si>
   <si>
     <t>4000,400,400</t>
   </si>
   <si>
-    <t>anyu460</t>
+    <t>anyu461</t>
   </si>
   <si>
     <t>20000,2000,1600</t>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="501">
   <si>
     <t>#</t>
   </si>
@@ -187,16 +187,16 @@
     <t>10000,1000,800</t>
   </si>
   <si>
-    <t>tt459</t>
+    <t>tt461</t>
   </si>
   <si>
     <t>9,5,9,4</t>
   </si>
   <si>
-    <t>4003,4004,4013,88</t>
-  </si>
-  <si>
-    <t>40000,4000,4000,6</t>
+    <t>4003,4004,4013,305</t>
+  </si>
+  <si>
+    <t>40000,4000,4000,2</t>
   </si>
   <si>
     <t>anyult24kbc</t>
@@ -2949,12 +2949,6 @@
       <c r="H23" s="9"/>
     </row>
     <row r="24" customHeight="1" spans="1:9">
-      <c r="A24" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>0</v>
-      </c>
       <c r="C24" s="6">
         <v>99</v>
       </c>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="501">
   <si>
     <t>#</t>
   </si>
@@ -2949,6 +2949,12 @@
       <c r="H23" s="9"/>
     </row>
     <row r="24" customHeight="1" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>0</v>
+      </c>
       <c r="C24" s="6">
         <v>99</v>
       </c>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -169,13 +169,13 @@
     <t>之后的及时删除</t>
   </si>
   <si>
-    <t>gx461</t>
+    <t>gx462</t>
   </si>
   <si>
     <t>4000,400,400</t>
   </si>
   <si>
-    <t>anyu461</t>
+    <t>anyu462</t>
   </si>
   <si>
     <t>20000,2000,1600</t>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -181,7 +181,7 @@
     <t>20000,2000,1600</t>
   </si>
   <si>
-    <t>1012026</t>
+    <t>bc462</t>
   </si>
   <si>
     <t>10000,1000,800</t>
@@ -2917,7 +2917,7 @@
       <c r="D17" s="6">
         <v>1</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="6" t="s">
         <v>35</v>
       </c>
       <c r="F17" s="14" t="s">
